--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251003_182906.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251003_182906.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251003_182906.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251003_182906.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
